--- a/artfynd/S 535-2025 artfynd.xlsx
+++ b/artfynd/S 535-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AZ49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885188</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126514986</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126344162</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120469321</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126510468</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126515805</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885178</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126512038</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885161</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,6 +1696,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885166</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1743,6 +1798,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885168</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1840,6 +1900,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885170</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1937,6 +2002,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885174</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2034,6 +2104,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885175</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2131,6 +2206,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885177</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2228,6 +2308,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885182</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2325,6 +2410,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885186</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2422,6 +2512,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885189</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2519,6 +2614,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885192</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2616,6 +2716,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885193</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2713,6 +2818,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885196</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2810,6 +2920,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885197</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2907,6 +3022,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885198</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3004,6 +3124,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885201</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3101,6 +3226,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885202</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3198,6 +3328,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885205</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3295,6 +3430,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885206</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3392,6 +3532,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885208</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3504,6 +3649,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126629778</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3611,6 +3761,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126629862</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3718,6 +3873,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126629920</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3825,6 +3985,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126629928</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3932,6 +4097,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126630302</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4039,6 +4209,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126630432</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4136,6 +4311,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885169</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4233,6 +4413,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885173</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4330,6 +4515,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885176</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4427,6 +4617,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885184</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4524,6 +4719,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885185</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4621,6 +4821,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885190</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4718,6 +4923,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885194</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4815,6 +5025,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885200</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4912,6 +5127,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885204</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5009,6 +5229,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885187</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5106,6 +5331,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885195</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5212,6 +5442,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126512411</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5309,6 +5544,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95885167</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5406,8 +5646,63 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126344142</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>